--- a/app/timesheet-app/public/2026_01 Conarum Timesheet BTP - Cuong Nguyen.xlsx
+++ b/app/timesheet-app/public/2026_01 Conarum Timesheet BTP - Cuong Nguyen.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr hidePivotFieldList="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learning\timesheet-management\app\timesheet-app\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF96C133-FD42-4CD0-A887-28C3E0889601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Title" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="4" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,12 +38,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C13" authorId="0">
+    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -556,20 +562,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="10">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="[$-409]mmmm\-yy"/>
-    <numFmt numFmtId="179" formatCode="mmmm\ yyyy"/>
-    <numFmt numFmtId="180" formatCode="[$-409]d\-mmm;@"/>
-    <numFmt numFmtId="181" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="182" formatCode="0.0"/>
-    <numFmt numFmtId="183" formatCode="d/m"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="166" formatCode="[$-409]mmmm\-yy"/>
+    <numFmt numFmtId="167" formatCode="mmmm\ yyyy"/>
+    <numFmt numFmtId="168" formatCode="[$-409]d\-mmm;@"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="d/m"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -700,157 +702,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -862,7 +713,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -899,194 +750,8 @@
         <bgColor rgb="FFE5B8B7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="29">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1332,262 +997,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1597,22 +1016,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1622,7 +1038,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1632,7 +1048,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1644,14 +1060,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1661,16 +1072,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1734,179 +1139,76 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="58" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="58" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1914,6 +1216,84 @@
           <bgColor rgb="FF8DB3E2"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1951,12 +1331,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
@@ -1967,11 +1350,17 @@
     <xdr:ext cx="1428750" cy="361950"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image2.png"/>
+        <xdr:cNvPr id="2" name="image2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1993,7 +1382,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -2004,11 +1393,17 @@
     <xdr:ext cx="1733550" cy="355600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image1.png"/>
+        <xdr:cNvPr id="2" name="image1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2030,102 +1425,25 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedVersion="5" refreshedDate="46051.6115740741" refreshedBy="ThinkPad" recordCount="46">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="ThinkPad" refreshedDate="46085.381107407411" refreshedVersion="8" recordCount="46" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B13:H59" sheet="Jan"/>
   </cacheSource>
   <cacheFields count="7">
-    <cacheField name="Date" numFmtId="180">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNonDate="0" containsDate="1" minDate="2025-01-01T00:00:00" maxDate="2025-12-30T00:00:00" count="22">
-        <d v="2025-12-30T00:00:00"/>
-        <d v="2025-01-01T00:00:00"/>
-        <d v="2025-01-02T00:00:00"/>
-        <d v="2025-01-03T00:00:00"/>
-        <d v="2025-01-04T00:00:00"/>
-        <d v="2025-01-05T00:00:00"/>
-        <d v="2025-01-06T00:00:00"/>
-        <d v="2025-01-08T00:00:00"/>
-        <d v="2025-01-09T00:00:00"/>
-        <d v="2025-01-12T00:00:00"/>
-        <d v="2025-01-13T00:00:00"/>
-        <d v="2025-01-14T00:00:00"/>
-        <d v="2025-01-15T00:00:00"/>
-        <d v="2025-01-16T00:00:00"/>
-        <d v="2025-01-18T00:00:00"/>
-        <d v="2025-01-19T00:00:00"/>
-        <d v="2025-01-20T00:00:00"/>
-        <d v="2025-01-21T00:00:00"/>
-        <d v="2025-01-22T00:00:00"/>
-        <d v="2025-01-23T00:00:00"/>
-        <d v="2025-01-26T00:00:00"/>
-        <d v="2025-01-27T00:00:00"/>
-      </sharedItems>
+    <cacheField name="Date" numFmtId="168">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-01-01T00:00:00" maxDate="2025-12-31T00:00:00"/>
     </cacheField>
     <cacheField name="Type" numFmtId="0">
-      <sharedItems count="2">
-        <s v="Papierkram"/>
-        <s v="Others"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Task" numFmtId="0">
-      <sharedItems count="35">
-        <s v="[Meeting] Catch-Up Status"/>
-        <s v="[Development] UI Improvements"/>
-        <s v="[Development] Intergrate Status Matrix"/>
-        <s v="[Development] Fix Status Matrix Bugs Based on Button Actions"/>
-        <s v="[Development] Implement Dialog for Activity App (Worklist &amp; Detail)"/>
-        <s v="[Development] Implement Dialog for Activity App (Create &amp; Filter)"/>
-        <s v="[Meeting] Brose Certificate Management"/>
-        <s v="[Development] Improve UI for Document Settings App (Field &amp; Category Definitions)"/>
-        <s v="[Development] Integrate CRUD API for Document Types"/>
-        <s v="[Meeting] Small ball dev 2026"/>
-        <s v="[Training] CPI Training Program - Meeting Request"/>
-        <s v="[Development] Improve Document Settings UI"/>
-        <s v="[Development] Implement Infinite Scrolling for Task and Activity Lists"/>
-        <s v="[Development] Implement Document and Attachment Upload"/>
-        <s v="[Development] Automatically Add Task Node to Task Flow upon Creation"/>
-        <s v="[Development] Implement Dynamic Field Insertion into Additional Data"/>
-        <s v="[Fix Bug ] Resolve Issues in Activity Worklist and Creation Popup"/>
-        <s v="[Meeting ] Brose Certificate - Discuss for Auhthorization topic"/>
-        <s v="[Development] Fix Multilingual Display Issues for Technical Fields"/>
-        <s v="[Development] Implement Actions for Task Card Buttons (Open, Edit, Add, Delete)"/>
-        <s v="[Development] Integrate Task Card APIs for Open, Edit, Add, and Delete Actions"/>
-        <s v="[Meeting ] Catch-Up Status"/>
-        <s v="[Meeting ] Year-End Review &amp; 2026 Kick-off – conarum Vietnam"/>
-        <s v="[Meeting ] Coordination Meeting 10: Certificate Management at Brose"/>
-        <s v="[Development] Persist User Input Data to Local Storage (Activity Details &amp; Create Activity)"/>
-        <s v="[Development] Build Design System for Activity Theme, Colors, and Fonts Configuration"/>
-        <s v="[Development] Persist User Input Data to Local Storage (Task Details &amp; Create Task)"/>
-        <s v="[Development ] Intergrate Button Back &amp; Reload Into Portal"/>
-        <s v="[Development] Clear Draft Data from Local Storage on Page Reload (Create Activity &amp; Task)"/>
-        <s v="[Fix Bug ] Resolve Multilingual and Date/Time Format Issues in Activity &amp; Task App"/>
-        <s v="[Training ] BTP AI Development"/>
-        <s v="[Development] Integrate Drag &amp; Drop for Task Flow"/>
-        <s v="[Training ] conarum Vietnam - CAP Training batch 01/2026"/>
-        <s v="[Meeting ] Discuss for outcomes &amp; estimation for next sprints"/>
-        <s v="[Development ] Intergrate Drag &amp; Drop For Taskflow"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="onsite" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Hours" numFmtId="181">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="8" count="12">
-        <n v="0.5"/>
-        <n v="7.5"/>
-        <n v="8"/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="6.5"/>
-        <n v="2"/>
-        <n v="4"/>
-        <n v="7"/>
-        <n v="6"/>
-        <n v="1.5"/>
-        <n v="4.5"/>
-      </sharedItems>
+    <cacheField name="Hours" numFmtId="169">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="8"/>
     </cacheField>
     <cacheField name="Project(Papierkram)" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
@@ -2135,484 +1453,445 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Note (Internal Projects name)" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="46">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="46">
   <r>
+    <d v="2025-12-30T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting] Catch-Up Status"/>
+    <m/>
+    <n v="0.5"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
+    <d v="2025-12-30T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] UI Improvements"/>
+    <m/>
+    <n v="7.5"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="1"/>
+    <d v="2025-01-01T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting] Catch-Up Status"/>
+    <m/>
+    <n v="0.5"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="1"/>
+    <d v="2025-01-01T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Intergrate Status Matrix"/>
+    <m/>
+    <n v="7.5"/>
     <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="2"/>
+    <d v="2025-01-02T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Fix Status Matrix Bugs Based on Button Actions"/>
+    <m/>
+    <n v="8"/>
     <x v="0"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="3"/>
+    <d v="2025-01-03T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting] Catch-Up Status"/>
+    <m/>
+    <n v="0.5"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="3"/>
+    <d v="2025-01-03T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Implement Dialog for Activity App (Worklist &amp; Detail)"/>
+    <m/>
+    <n v="7.5"/>
     <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="4"/>
+    <d v="2025-01-04T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Implement Dialog for Activity App (Create &amp; Filter)"/>
+    <m/>
+    <n v="8"/>
     <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="5"/>
+    <d v="2025-01-05T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting] Brose Certificate Management"/>
+    <m/>
+    <n v="0.5"/>
     <x v="0"/>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="5"/>
+    <d v="2025-01-05T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Improve UI for Document Settings App (Field &amp; Category Definitions)"/>
+    <m/>
+    <n v="7.5"/>
     <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="6"/>
+    <d v="2025-01-06T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting] Catch-Up Status"/>
+    <m/>
+    <n v="0.5"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="6"/>
+    <d v="2025-01-06T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Integrate CRUD API for Document Types"/>
+    <m/>
+    <n v="7.5"/>
     <x v="0"/>
-    <x v="8"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="7"/>
+    <d v="2025-01-08T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Meeting] Small ball dev 2026"/>
+    <m/>
+    <n v="1"/>
     <x v="1"/>
-    <x v="9"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="7"/>
+    <d v="2025-01-08T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting] Catch-Up Status"/>
+    <m/>
+    <n v="0.5"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="7"/>
+    <d v="2025-01-08T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Training] CPI Training Program - Meeting Request"/>
+    <m/>
+    <n v="3"/>
     <x v="1"/>
-    <x v="10"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="7"/>
+    <d v="2025-01-08T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Improve Document Settings UI"/>
+    <m/>
+    <n v="6.5"/>
     <x v="0"/>
-    <x v="11"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="8"/>
+    <d v="2025-01-09T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Implement Infinite Scrolling for Task and Activity Lists"/>
+    <m/>
+    <n v="2"/>
     <x v="0"/>
-    <x v="12"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="8"/>
+    <d v="2025-01-09T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Implement Document and Attachment Upload"/>
+    <m/>
+    <n v="2"/>
     <x v="0"/>
-    <x v="13"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="8"/>
+    <d v="2025-01-09T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Automatically Add Task Node to Task Flow upon Creation"/>
+    <m/>
+    <n v="4"/>
     <x v="0"/>
-    <x v="14"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="9"/>
+    <d v="2025-01-12T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Implement Dynamic Field Insertion into Additional Data"/>
+    <m/>
+    <n v="8"/>
     <x v="0"/>
-    <x v="15"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="9"/>
+    <d v="2025-01-12T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Training] CPI Training Program - Meeting Request"/>
+    <m/>
+    <n v="3"/>
     <x v="1"/>
-    <x v="10"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="10"/>
+    <d v="2025-01-13T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Fix Bug ] Resolve Issues in Activity Worklist and Creation Popup"/>
+    <m/>
+    <n v="4"/>
     <x v="0"/>
-    <x v="16"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="10"/>
+    <d v="2025-01-13T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting ] Brose Certificate - Discuss for Auhthorization topic"/>
+    <m/>
+    <n v="2"/>
     <x v="0"/>
-    <x v="17"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="10"/>
+    <d v="2025-01-13T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Fix Multilingual Display Issues for Technical Fields"/>
+    <m/>
+    <n v="2"/>
     <x v="0"/>
-    <x v="18"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="11"/>
+    <d v="2025-01-14T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Implement Actions for Task Card Buttons (Open, Edit, Add, Delete)"/>
+    <m/>
+    <n v="8"/>
     <x v="0"/>
-    <x v="19"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="12"/>
+    <d v="2025-01-15T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Integrate Task Card APIs for Open, Edit, Add, and Delete Actions"/>
+    <m/>
+    <n v="7"/>
     <x v="0"/>
-    <x v="20"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="12"/>
+    <d v="2025-01-15T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting ] Catch-Up Status"/>
+    <m/>
+    <n v="1"/>
     <x v="0"/>
-    <x v="21"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="13"/>
+    <d v="2025-01-16T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Meeting ] Year-End Review &amp; 2026 Kick-off – conarum Vietnam"/>
+    <m/>
+    <n v="1"/>
     <x v="1"/>
-    <x v="22"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="13"/>
+    <d v="2025-01-16T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting ] Coordination Meeting 10: Certificate Management at Brose"/>
+    <m/>
+    <n v="1"/>
     <x v="0"/>
-    <x v="23"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="13"/>
+    <d v="2025-01-16T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Persist User Input Data to Local Storage (Activity Details &amp; Create Activity)"/>
+    <m/>
+    <n v="6"/>
     <x v="0"/>
-    <x v="24"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="14"/>
+    <d v="2025-01-18T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Development] Build Design System for Activity Theme, Colors, and Fonts Configuration"/>
+    <m/>
+    <n v="4"/>
     <x v="1"/>
-    <x v="25"/>
-    <x v="0"/>
-    <x v="7"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="15"/>
+    <d v="2025-01-19T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Training] CPI Training Program - Meeting Request"/>
+    <m/>
+    <n v="3"/>
     <x v="1"/>
-    <x v="10"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="15"/>
+    <d v="2025-01-19T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Persist User Input Data to Local Storage (Task Details &amp; Create Task)"/>
+    <m/>
+    <n v="8"/>
     <x v="0"/>
-    <x v="26"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="16"/>
+    <d v="2025-01-20T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting ] Catch-Up Status"/>
+    <m/>
+    <n v="1"/>
     <x v="0"/>
-    <x v="21"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="16"/>
+    <d v="2025-01-20T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development ] Intergrate Button Back &amp; Reload Into Portal"/>
+    <m/>
+    <n v="7"/>
     <x v="0"/>
-    <x v="27"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="17"/>
+    <d v="2025-01-21T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Clear Draft Data from Local Storage on Page Reload (Create Activity &amp; Task)"/>
+    <m/>
+    <n v="8"/>
     <x v="0"/>
-    <x v="28"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="18"/>
+    <d v="2025-01-22T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting ] Catch-Up Status"/>
+    <m/>
+    <n v="1"/>
     <x v="0"/>
-    <x v="21"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="18"/>
+    <d v="2025-01-22T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Fix Bug ] Resolve Multilingual and Date/Time Format Issues in Activity &amp; Task App"/>
+    <m/>
+    <n v="7"/>
     <x v="0"/>
-    <x v="29"/>
-    <x v="0"/>
-    <x v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="18"/>
+    <d v="2025-01-22T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Training] CPI Training Program - Meeting Request"/>
+    <m/>
+    <n v="3"/>
     <x v="1"/>
-    <x v="10"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="19"/>
+    <d v="2025-01-23T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Training ] BTP AI Development"/>
+    <m/>
+    <n v="2"/>
     <x v="1"/>
-    <x v="30"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="20"/>
+    <d v="2025-01-26T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development] Integrate Drag &amp; Drop for Task Flow"/>
+    <m/>
+    <n v="8"/>
     <x v="0"/>
-    <x v="31"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="21"/>
+    <d v="2025-01-27T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Training ] conarum Vietnam - CAP Training batch 01/2026"/>
+    <m/>
+    <n v="1.5"/>
     <x v="1"/>
-    <x v="32"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="21"/>
+    <d v="2025-01-27T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting ] Discuss for outcomes &amp; estimation for next sprints"/>
+    <m/>
+    <n v="0.5"/>
     <x v="0"/>
-    <x v="33"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="21"/>
+    <d v="2025-01-27T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Meeting] Catch-Up Status"/>
+    <m/>
+    <n v="0.5"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="21"/>
+    <d v="2025-01-27T00:00:00"/>
+    <s v="Papierkram"/>
+    <s v="[Development ] Intergrate Drag &amp; Drop For Taskflow"/>
+    <m/>
+    <n v="4.5"/>
     <x v="0"/>
-    <x v="34"/>
-    <x v="0"/>
-    <x v="11"/>
-    <x v="0"/>
-    <x v="0"/>
+    <m/>
   </r>
   <r>
-    <x v="21"/>
+    <d v="2025-01-27T00:00:00"/>
+    <s v="Others"/>
+    <s v="[Training ] conarum Vietnam - CAP Training batch 01/2026"/>
+    <m/>
+    <n v="1"/>
     <x v="1"/>
-    <x v="32"/>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="June" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="" updatedVersion="5" compact="0" compactData="0" showDrill="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="June" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="" updatedVersion="8" compact="0" compactData="0">
   <location ref="J1:K4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" numFmtId="183" showAll="0">
-      <items count="23">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField compact="0" numFmtId="171" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
         <item m="1" x="2"/>
@@ -2643,19 +1922,24 @@
   <dataFields count="1">
     <dataField name="Sum of Hours" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_1" displayName="Table_1" ref="B2:G46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B2:G46">
   <tableColumns count="6">
-    <tableColumn id="1" name="Customer" dataDxfId="0"/>
-    <tableColumn id="2" name="Papierkram/Project Code" dataDxfId="1"/>
-    <tableColumn id="3" name="Project Name" dataDxfId="2"/>
-    <tableColumn id="4" name="Active" dataDxfId="3"/>
-    <tableColumn id="5" name="Project Manager" dataDxfId="4"/>
-    <tableColumn id="6" name="Note" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Customer" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Papierkram/Project Code" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Project Name" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Active" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Project Manager" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Note" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="legend-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2853,402 +2137,402 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AJ1000"/>
-  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="7" width="3.57" customWidth="1"/>
-    <col min="8" max="8" width="7.86" customWidth="1"/>
-    <col min="9" max="23" width="3.57" customWidth="1"/>
-    <col min="24" max="24" width="5.57" customWidth="1"/>
-    <col min="25" max="36" width="3.57" customWidth="1"/>
+    <col min="1" max="7" width="3.5546875" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" customWidth="1"/>
+    <col min="9" max="23" width="3.5546875" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" customWidth="1"/>
+    <col min="25" max="36" width="3.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1"/>
-    <row r="2" ht="12.75" customHeight="1" spans="2:5">
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="E2" s="78"/>
-    </row>
-    <row r="3" ht="12" customHeight="1" spans="2:25">
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="Y3" s="45"/>
-    </row>
-    <row r="4" ht="12.75" customHeight="1" spans="8:31">
-      <c r="H4" s="79" t="s">
+    <row r="1" spans="2:31" ht="12.75" customHeight="1"/>
+    <row r="2" spans="2:31" ht="12.75" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="E2" s="64"/>
+    </row>
+    <row r="3" spans="2:31" ht="12" customHeight="1">
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="Y3" s="35"/>
+    </row>
+    <row r="4" spans="2:31" ht="12.75" customHeight="1">
+      <c r="H4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="80"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
-      <c r="AB4" s="80"/>
-      <c r="AC4" s="80"/>
-      <c r="AD4" s="80"/>
-      <c r="AE4" s="80"/>
-    </row>
-    <row r="5" ht="12.75" customHeight="1" spans="4:31">
-      <c r="D5" s="78"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="80"/>
-      <c r="T5" s="80"/>
-      <c r="U5" s="80"/>
-      <c r="V5" s="80"/>
-      <c r="W5" s="80"/>
-      <c r="X5" s="80"/>
-      <c r="Y5" s="80"/>
-      <c r="Z5" s="80"/>
-      <c r="AA5" s="80"/>
-      <c r="AB5" s="80"/>
-      <c r="AC5" s="80"/>
-      <c r="AD5" s="80"/>
-      <c r="AE5" s="80"/>
-    </row>
-    <row r="6" ht="12" customHeight="1" spans="4:31">
-      <c r="D6" s="78"/>
-      <c r="AA6" s="93" t="s">
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="66"/>
+      <c r="Y4" s="66"/>
+      <c r="Z4" s="66"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+    </row>
+    <row r="5" spans="2:31" ht="12.75" customHeight="1">
+      <c r="D5" s="64"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="66"/>
+      <c r="U5" s="66"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="66"/>
+      <c r="X5" s="66"/>
+      <c r="Y5" s="66"/>
+      <c r="Z5" s="66"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+    </row>
+    <row r="6" spans="2:31" ht="12" customHeight="1">
+      <c r="D6" s="64"/>
+      <c r="AA6" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="AB6" s="80"/>
-      <c r="AC6" s="80"/>
-      <c r="AD6" s="94">
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="67">
         <v>1.2</v>
       </c>
-      <c r="AE6" s="80"/>
-    </row>
-    <row r="7" ht="12.75" customHeight="1"/>
-    <row r="8" ht="12.75" customHeight="1"/>
-    <row r="9" ht="12" customHeight="1"/>
-    <row r="10" ht="12" customHeight="1"/>
-    <row r="11" ht="12" customHeight="1"/>
-    <row r="12" ht="12" customHeight="1"/>
-    <row r="13" ht="12" customHeight="1" spans="8:31">
-      <c r="H13" s="81" t="s">
+      <c r="AE6" s="66"/>
+    </row>
+    <row r="7" spans="2:31" ht="12.75" customHeight="1"/>
+    <row r="8" spans="2:31" ht="12.75" customHeight="1"/>
+    <row r="9" spans="2:31" ht="12" customHeight="1"/>
+    <row r="10" spans="2:31" ht="12" customHeight="1"/>
+    <row r="11" spans="2:31" ht="12" customHeight="1"/>
+    <row r="12" spans="2:31" ht="12" customHeight="1"/>
+    <row r="13" spans="2:31" ht="12" customHeight="1">
+      <c r="H13" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="I13" s="87"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="88"/>
-      <c r="L13" s="81" t="s">
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="M13" s="87"/>
-      <c r="N13" s="88"/>
-      <c r="O13" s="81" t="s">
+      <c r="M13" s="69"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="P13" s="87"/>
-      <c r="Q13" s="88"/>
-      <c r="R13" s="81" t="s">
+      <c r="P13" s="69"/>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="S13" s="87"/>
-      <c r="T13" s="87"/>
-      <c r="U13" s="87"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="87"/>
-      <c r="X13" s="87"/>
-      <c r="Y13" s="87"/>
-      <c r="Z13" s="87"/>
-      <c r="AA13" s="87"/>
-      <c r="AB13" s="87"/>
-      <c r="AC13" s="87"/>
-      <c r="AD13" s="87"/>
-      <c r="AE13" s="88"/>
-    </row>
-    <row r="14" ht="12" customHeight="1" spans="8:31">
-      <c r="H14" s="82">
+      <c r="S13" s="69"/>
+      <c r="T13" s="69"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="69"/>
+      <c r="W13" s="69"/>
+      <c r="X13" s="69"/>
+      <c r="Y13" s="69"/>
+      <c r="Z13" s="69"/>
+      <c r="AA13" s="69"/>
+      <c r="AB13" s="69"/>
+      <c r="AC13" s="69"/>
+      <c r="AD13" s="69"/>
+      <c r="AE13" s="70"/>
+    </row>
+    <row r="14" spans="2:31" ht="12" customHeight="1">
+      <c r="H14" s="71">
         <v>45873</v>
       </c>
-      <c r="I14" s="87"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="89" t="s">
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="M14" s="87"/>
-      <c r="N14" s="88"/>
-      <c r="O14" s="89" t="s">
+      <c r="M14" s="69"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="88"/>
-      <c r="R14" s="89" t="s">
+      <c r="P14" s="69"/>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="87"/>
-      <c r="T14" s="87"/>
-      <c r="U14" s="87"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="87"/>
-      <c r="X14" s="87"/>
-      <c r="Y14" s="87"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="87"/>
-      <c r="AB14" s="87"/>
-      <c r="AC14" s="87"/>
-      <c r="AD14" s="87"/>
-      <c r="AE14" s="88"/>
-    </row>
-    <row r="15" ht="12" customHeight="1" spans="8:31">
-      <c r="H15" s="83">
+      <c r="S14" s="69"/>
+      <c r="T14" s="69"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="69"/>
+      <c r="W14" s="69"/>
+      <c r="X14" s="69"/>
+      <c r="Y14" s="69"/>
+      <c r="Z14" s="69"/>
+      <c r="AA14" s="69"/>
+      <c r="AB14" s="69"/>
+      <c r="AC14" s="69"/>
+      <c r="AD14" s="69"/>
+      <c r="AE14" s="70"/>
+    </row>
+    <row r="15" spans="2:31" ht="12" customHeight="1">
+      <c r="H15" s="73">
         <v>45694</v>
       </c>
-      <c r="I15" s="87"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="90" t="s">
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="M15" s="87"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="89" t="s">
+      <c r="M15" s="69"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="P15" s="87"/>
-      <c r="Q15" s="88"/>
-      <c r="R15" s="89" t="s">
+      <c r="P15" s="69"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="S15" s="87"/>
-      <c r="T15" s="87"/>
-      <c r="U15" s="87"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="87"/>
-      <c r="X15" s="87"/>
-      <c r="Y15" s="87"/>
-      <c r="Z15" s="87"/>
-      <c r="AA15" s="87"/>
-      <c r="AB15" s="87"/>
-      <c r="AC15" s="87"/>
-      <c r="AD15" s="87"/>
-      <c r="AE15" s="88"/>
-    </row>
-    <row r="16" ht="12" customHeight="1"/>
-    <row r="17" ht="12" customHeight="1" spans="8:31">
-      <c r="H17" s="81" t="s">
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="69"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="69"/>
+      <c r="AC15" s="69"/>
+      <c r="AD15" s="69"/>
+      <c r="AE15" s="70"/>
+    </row>
+    <row r="16" spans="2:31" ht="12" customHeight="1"/>
+    <row r="17" spans="5:31" ht="12" customHeight="1">
+      <c r="H17" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="87"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="81" t="s">
+      <c r="I17" s="69"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="L17" s="87"/>
-      <c r="M17" s="87"/>
-      <c r="N17" s="87"/>
-      <c r="O17" s="87"/>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="87"/>
-      <c r="V17" s="87"/>
-      <c r="W17" s="87"/>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="87"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87"/>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="87"/>
-      <c r="AD17" s="87"/>
-      <c r="AE17" s="88"/>
-    </row>
-    <row r="18" ht="12" customHeight="1" spans="8:31">
-      <c r="H18" s="84" t="s">
+      <c r="L17" s="69"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="69"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="69"/>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="69"/>
+      <c r="AC17" s="69"/>
+      <c r="AD17" s="69"/>
+      <c r="AE17" s="70"/>
+    </row>
+    <row r="18" spans="5:31" ht="12" customHeight="1">
+      <c r="H18" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="I18" s="87"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="91" t="s">
+      <c r="I18" s="69"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="L18" s="87"/>
-      <c r="M18" s="87"/>
-      <c r="N18" s="87"/>
-      <c r="O18" s="87"/>
-      <c r="P18" s="87"/>
-      <c r="Q18" s="87"/>
-      <c r="R18" s="87"/>
-      <c r="S18" s="87"/>
-      <c r="T18" s="87"/>
-      <c r="U18" s="87"/>
-      <c r="V18" s="87"/>
-      <c r="W18" s="87"/>
-      <c r="X18" s="87"/>
-      <c r="Y18" s="87"/>
-      <c r="Z18" s="87"/>
-      <c r="AA18" s="87"/>
-      <c r="AB18" s="87"/>
-      <c r="AC18" s="87"/>
-      <c r="AD18" s="87"/>
-      <c r="AE18" s="88"/>
-    </row>
-    <row r="19" ht="33" customHeight="1" spans="5:31">
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="H19" s="85" t="s">
+      <c r="L18" s="69"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="69"/>
+      <c r="R18" s="69"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="69"/>
+      <c r="U18" s="69"/>
+      <c r="V18" s="69"/>
+      <c r="W18" s="69"/>
+      <c r="X18" s="69"/>
+      <c r="Y18" s="69"/>
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="69"/>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="69"/>
+      <c r="AE18" s="70"/>
+    </row>
+    <row r="19" spans="5:31" ht="33" customHeight="1">
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="H19" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="87"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="92" t="s">
+      <c r="I19" s="69"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="L19" s="87"/>
-      <c r="M19" s="87"/>
-      <c r="N19" s="87"/>
-      <c r="O19" s="87"/>
-      <c r="P19" s="87"/>
-      <c r="Q19" s="87"/>
-      <c r="R19" s="87"/>
-      <c r="S19" s="87"/>
-      <c r="T19" s="87"/>
-      <c r="U19" s="87"/>
-      <c r="V19" s="87"/>
-      <c r="W19" s="87"/>
-      <c r="X19" s="87"/>
-      <c r="Y19" s="87"/>
-      <c r="Z19" s="87"/>
-      <c r="AA19" s="87"/>
-      <c r="AB19" s="87"/>
-      <c r="AC19" s="87"/>
-      <c r="AD19" s="87"/>
-      <c r="AE19" s="88"/>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="8:31">
-      <c r="H20" s="86" t="s">
+      <c r="L19" s="69"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="69"/>
+      <c r="T19" s="69"/>
+      <c r="U19" s="69"/>
+      <c r="V19" s="69"/>
+      <c r="W19" s="69"/>
+      <c r="X19" s="69"/>
+      <c r="Y19" s="69"/>
+      <c r="Z19" s="69"/>
+      <c r="AA19" s="69"/>
+      <c r="AB19" s="69"/>
+      <c r="AC19" s="69"/>
+      <c r="AD19" s="69"/>
+      <c r="AE19" s="70"/>
+    </row>
+    <row r="20" spans="5:31" ht="36" customHeight="1">
+      <c r="H20" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="87"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="92" t="s">
+      <c r="I20" s="69"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="L20" s="87"/>
-      <c r="M20" s="87"/>
-      <c r="N20" s="87"/>
-      <c r="O20" s="87"/>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="87"/>
-      <c r="W20" s="87"/>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="87"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-      <c r="AD20" s="87"/>
-      <c r="AE20" s="88"/>
-    </row>
-    <row r="21" ht="12" customHeight="1"/>
-    <row r="22" ht="28.5" customHeight="1"/>
-    <row r="23" ht="12" customHeight="1"/>
-    <row r="24" ht="12" customHeight="1"/>
-    <row r="25" ht="12" customHeight="1"/>
-    <row r="26" ht="12" customHeight="1"/>
-    <row r="27" ht="12" customHeight="1"/>
-    <row r="28" ht="12" customHeight="1"/>
-    <row r="29" ht="12" customHeight="1"/>
-    <row r="30" ht="12" customHeight="1"/>
-    <row r="31" ht="12" customHeight="1"/>
-    <row r="32" ht="12" customHeight="1"/>
-    <row r="33" ht="12" customHeight="1"/>
-    <row r="34" ht="12" customHeight="1"/>
-    <row r="35" ht="12" customHeight="1" spans="30:36">
-      <c r="AD35" s="45"/>
-      <c r="AE35" s="2"/>
-      <c r="AF35" s="2"/>
-      <c r="AG35" s="2"/>
-      <c r="AH35" s="2"/>
-      <c r="AI35" s="2"/>
-      <c r="AJ35" s="2"/>
-    </row>
-    <row r="36" ht="12" customHeight="1"/>
-    <row r="37" ht="12" customHeight="1" spans="2:35">
-      <c r="B37" s="78"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="78"/>
-      <c r="N37" s="78"/>
-      <c r="O37" s="78"/>
-      <c r="P37" s="78"/>
-      <c r="Q37" s="78"/>
-      <c r="R37" s="78"/>
-      <c r="S37" s="78"/>
-      <c r="T37" s="78"/>
-      <c r="U37" s="78"/>
-      <c r="V37" s="78"/>
-      <c r="W37" s="78"/>
-      <c r="X37" s="78"/>
-      <c r="Y37" s="78"/>
-      <c r="Z37" s="78"/>
-      <c r="AA37" s="78"/>
-      <c r="AB37" s="78"/>
-      <c r="AC37" s="78"/>
-      <c r="AD37" s="78"/>
-      <c r="AE37" s="78"/>
-      <c r="AF37" s="78"/>
-      <c r="AG37" s="78"/>
-      <c r="AH37" s="78"/>
-      <c r="AI37" s="78"/>
-    </row>
-    <row r="38" ht="12" customHeight="1"/>
-    <row r="39" ht="12" customHeight="1"/>
-    <row r="40" ht="12" customHeight="1"/>
-    <row r="41" ht="12" customHeight="1"/>
-    <row r="42" ht="12" customHeight="1"/>
-    <row r="43" ht="12" customHeight="1"/>
-    <row r="44" ht="12" customHeight="1"/>
-    <row r="45" ht="12" customHeight="1"/>
-    <row r="46" ht="12" customHeight="1"/>
-    <row r="47" ht="12" customHeight="1"/>
-    <row r="48" ht="12" customHeight="1"/>
+      <c r="L20" s="69"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="69"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="69"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="69"/>
+      <c r="W20" s="69"/>
+      <c r="X20" s="69"/>
+      <c r="Y20" s="69"/>
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="69"/>
+      <c r="AC20" s="69"/>
+      <c r="AD20" s="69"/>
+      <c r="AE20" s="70"/>
+    </row>
+    <row r="21" spans="5:31" ht="12" customHeight="1"/>
+    <row r="22" spans="5:31" ht="28.5" customHeight="1"/>
+    <row r="23" spans="5:31" ht="12" customHeight="1"/>
+    <row r="24" spans="5:31" ht="12" customHeight="1"/>
+    <row r="25" spans="5:31" ht="12" customHeight="1"/>
+    <row r="26" spans="5:31" ht="12" customHeight="1"/>
+    <row r="27" spans="5:31" ht="12" customHeight="1"/>
+    <row r="28" spans="5:31" ht="12" customHeight="1"/>
+    <row r="29" spans="5:31" ht="12" customHeight="1"/>
+    <row r="30" spans="5:31" ht="12" customHeight="1"/>
+    <row r="31" spans="5:31" ht="12" customHeight="1"/>
+    <row r="32" spans="5:31" ht="12" customHeight="1"/>
+    <row r="33" spans="2:36" ht="12" customHeight="1"/>
+    <row r="34" spans="2:36" ht="12" customHeight="1"/>
+    <row r="35" spans="2:36" ht="12" customHeight="1">
+      <c r="AD35" s="80"/>
+      <c r="AE35" s="81"/>
+      <c r="AF35" s="81"/>
+      <c r="AG35" s="81"/>
+      <c r="AH35" s="81"/>
+      <c r="AI35" s="81"/>
+      <c r="AJ35" s="81"/>
+    </row>
+    <row r="36" spans="2:36" ht="12" customHeight="1"/>
+    <row r="37" spans="2:36" ht="12" customHeight="1">
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="64"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="64"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="64"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="64"/>
+      <c r="S37" s="64"/>
+      <c r="T37" s="64"/>
+      <c r="U37" s="64"/>
+      <c r="V37" s="64"/>
+      <c r="W37" s="64"/>
+      <c r="X37" s="64"/>
+      <c r="Y37" s="64"/>
+      <c r="Z37" s="64"/>
+      <c r="AA37" s="64"/>
+      <c r="AB37" s="64"/>
+      <c r="AC37" s="64"/>
+      <c r="AD37" s="64"/>
+      <c r="AE37" s="64"/>
+      <c r="AF37" s="64"/>
+      <c r="AG37" s="64"/>
+      <c r="AH37" s="64"/>
+      <c r="AI37" s="64"/>
+    </row>
+    <row r="38" spans="2:36" ht="12" customHeight="1"/>
+    <row r="39" spans="2:36" ht="12" customHeight="1"/>
+    <row r="40" spans="2:36" ht="12" customHeight="1"/>
+    <row r="41" spans="2:36" ht="12" customHeight="1"/>
+    <row r="42" spans="2:36" ht="12" customHeight="1"/>
+    <row r="43" spans="2:36" ht="12" customHeight="1"/>
+    <row r="44" spans="2:36" ht="12" customHeight="1"/>
+    <row r="45" spans="2:36" ht="12" customHeight="1"/>
+    <row r="46" spans="2:36" ht="12" customHeight="1"/>
+    <row r="47" spans="2:36" ht="12" customHeight="1"/>
+    <row r="48" spans="2:36" ht="12" customHeight="1"/>
     <row r="49" ht="12" customHeight="1"/>
     <row r="50" ht="12" customHeight="1"/>
     <row r="51" ht="12" customHeight="1"/>
@@ -4203,12 +3487,16 @@
     <row r="1000" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="AA6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="R13:AE13"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="K20:AE20"/>
+    <mergeCell ref="AD35:AJ35"/>
+    <mergeCell ref="H4:AE5"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:AE17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:AE18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="K19:AE19"/>
     <mergeCell ref="H14:K14"/>
     <mergeCell ref="L14:N14"/>
     <mergeCell ref="O14:Q14"/>
@@ -4217,894 +3505,887 @@
     <mergeCell ref="L15:N15"/>
     <mergeCell ref="O15:Q15"/>
     <mergeCell ref="R15:AE15"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:AE17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:AE18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="K19:AE19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="K20:AE20"/>
-    <mergeCell ref="AD35:AJ35"/>
-    <mergeCell ref="H4:AE5"/>
+    <mergeCell ref="AA6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="R13:AE13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:G1000"/>
-  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.29" customWidth="1"/>
-    <col min="2" max="2" width="23.43" customWidth="1"/>
-    <col min="3" max="3" width="63.43" customWidth="1"/>
-    <col min="4" max="4" width="42.14" customWidth="1"/>
-    <col min="5" max="5" width="21.14" customWidth="1"/>
-    <col min="6" max="6" width="19.29" customWidth="1"/>
-    <col min="7" max="7" width="26.86" customWidth="1"/>
-    <col min="8" max="26" width="8.71" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="63.44140625" customWidth="1"/>
+    <col min="4" max="4" width="42.109375" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="26.88671875" customWidth="1"/>
+    <col min="8" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12" customHeight="1"/>
-    <row r="2" ht="12" customHeight="1" spans="2:7">
-      <c r="B2" s="54" t="s">
+    <row r="1" spans="2:7" ht="12" customHeight="1"/>
+    <row r="2" spans="2:7" ht="12" customHeight="1">
+      <c r="B2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="12" customHeight="1" spans="2:7">
-      <c r="B3" s="56" t="s">
+    <row r="3" spans="2:7" ht="12" customHeight="1">
+      <c r="B3" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="58" t="str">
+      <c r="D3" s="44" t="str">
         <f t="shared" ref="D3:D32" si="0">B3&amp;"-"&amp;C3</f>
         <v>Spirit/21-Schunk div. Papierkram Projects</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="57"/>
-    </row>
-    <row r="4" ht="12" customHeight="1" spans="2:7">
-      <c r="B4" s="56" t="s">
+      <c r="G3" s="43"/>
+    </row>
+    <row r="4" spans="2:7" ht="12" customHeight="1">
+      <c r="B4" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="58" t="str">
+      <c r="D4" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>Spirit/21-1286000-47040-01 - Spirit - Storopack Hans Reichenecker </v>
-      </c>
-      <c r="E4" s="59" t="s">
+        <v>Spirit/21-1286000-47040-01 - Spirit - Storopack Hans Reichenecker</v>
+      </c>
+      <c r="E4" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="57"/>
-    </row>
-    <row r="5" ht="12" customHeight="1" spans="2:7">
-      <c r="B5" s="56" t="s">
+      <c r="G4" s="43"/>
+    </row>
+    <row r="5" spans="2:7" ht="12" customHeight="1">
+      <c r="B5" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="58" t="str">
+      <c r="D5" s="44" t="str">
         <f t="shared" si="0"/>
         <v>KARON -2025_0001_KARON_EV_KNORR_BREMSE</v>
       </c>
-      <c r="E5" s="59" t="s">
+      <c r="E5" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="57"/>
-    </row>
-    <row r="6" ht="12" customHeight="1" spans="2:7">
-      <c r="B6" s="60" t="s">
+      <c r="G5" s="43"/>
+    </row>
+    <row r="6" spans="2:7" ht="12" customHeight="1">
+      <c r="B6" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="44" t="str">
         <f t="shared" si="0"/>
         <v>KARON -2025_0002_KARON_MAHLE</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="57"/>
-    </row>
-    <row r="7" ht="12" customHeight="1" spans="2:7">
-      <c r="B7" s="60" t="s">
+      <c r="G6" s="43"/>
+    </row>
+    <row r="7" spans="2:7" ht="12" customHeight="1">
+      <c r="B7" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="58" t="str">
+      <c r="D7" s="44" t="str">
         <f t="shared" si="0"/>
         <v>DNUS-proFRM</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="57"/>
-    </row>
-    <row r="8" ht="12" customHeight="1" spans="2:7">
-      <c r="B8" s="60" t="s">
+      <c r="G7" s="43"/>
+    </row>
+    <row r="8" spans="2:7" ht="12" customHeight="1">
+      <c r="B8" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="58" t="str">
+      <c r="D8" s="44" t="str">
         <f t="shared" si="0"/>
         <v>biotest-4530039906_10_biotest_2025: Support MM/SRM</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="57"/>
-    </row>
-    <row r="9" ht="12" customHeight="1" spans="2:7">
-      <c r="B9" s="60" t="s">
+      <c r="G8" s="43"/>
+    </row>
+    <row r="9" spans="2:7" ht="12" customHeight="1">
+      <c r="B9" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="58" t="str">
+      <c r="D9" s="44" t="str">
         <f t="shared" si="0"/>
         <v>manrolandgoss-4501144702 - SAP-Support</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="57"/>
-    </row>
-    <row r="10" ht="12" customHeight="1" spans="2:7">
-      <c r="B10" s="60" t="s">
+      <c r="G9" s="43"/>
+    </row>
+    <row r="10" spans="2:7" ht="12" customHeight="1">
+      <c r="B10" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="58" t="str">
+      <c r="D10" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>manrolandgoss-4501183526-10/20 - manrolandgoss level 2 </v>
-      </c>
-      <c r="E10" s="59" t="s">
+        <v>manrolandgoss-4501183526-10/20 - manrolandgoss level 2</v>
+      </c>
+      <c r="E10" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="57"/>
-    </row>
-    <row r="11" ht="12" customHeight="1" spans="2:7">
-      <c r="B11" s="60" t="s">
+      <c r="G10" s="43"/>
+    </row>
+    <row r="11" spans="2:7" ht="12" customHeight="1">
+      <c r="B11" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="58" t="str">
+      <c r="D11" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Bosch Rexorth-PR1-8320090824- DC - Grownfield S/4 HANA</v>
       </c>
-      <c r="E11" s="59" t="s">
+      <c r="E11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="57"/>
-    </row>
-    <row r="12" ht="12" customHeight="1" spans="2:7">
-      <c r="B12" s="60" t="s">
+      <c r="G11" s="43"/>
+    </row>
+    <row r="12" spans="2:7" ht="12" customHeight="1">
+      <c r="B12" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="58" t="str">
+      <c r="D12" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Wacker Chemie AG-9106075697- Support 2023</v>
       </c>
-      <c r="E12" s="59" t="s">
+      <c r="E12" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="57"/>
-    </row>
-    <row r="13" ht="12" customHeight="1" spans="2:7">
-      <c r="B13" s="60" t="s">
+      <c r="G12" s="43"/>
+    </row>
+    <row r="13" spans="2:7" ht="12" customHeight="1">
+      <c r="B13" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="58" t="str">
+      <c r="D13" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Wacker Chemie AG-9106701418 - Realisierung ERSA_FioriApp-ZMMP</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="57"/>
-    </row>
-    <row r="14" ht="12" customHeight="1" spans="2:7">
-      <c r="B14" s="60" t="s">
+      <c r="G13" s="43"/>
+    </row>
+    <row r="14" spans="2:7" ht="12" customHeight="1">
+      <c r="B14" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="58" t="str">
+      <c r="D14" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Wacker Chemie AG-9106884529 - Fiori App Interne Meldung</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="E14" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="57"/>
-    </row>
-    <row r="15" ht="12" customHeight="1" spans="2:7">
-      <c r="B15" s="60" t="s">
+      <c r="G14" s="43"/>
+    </row>
+    <row r="15" spans="2:7" ht="12" customHeight="1">
+      <c r="B15" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="58" t="str">
+      <c r="D15" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Siltronic-4501917977 - Support 2025</v>
       </c>
-      <c r="E15" s="59" t="s">
+      <c r="E15" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="57"/>
-    </row>
-    <row r="16" ht="12" customHeight="1" spans="2:7">
-      <c r="B16" s="60" t="s">
+      <c r="G15" s="43"/>
+    </row>
+    <row r="16" spans="2:7" ht="12" customHeight="1">
+      <c r="B16" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="58" t="str">
+      <c r="D16" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Uni Klinikum Düsseldorf UKD-Support 2025 Bestellung SAP kommt noch</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G16" s="57"/>
-    </row>
-    <row r="17" ht="12" customHeight="1" spans="2:7">
-      <c r="B17" s="60" t="s">
+      <c r="G16" s="43"/>
+    </row>
+    <row r="17" spans="2:7" ht="12" customHeight="1">
+      <c r="B17" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="58" t="str">
+      <c r="D17" s="44" t="str">
         <f t="shared" si="0"/>
         <v>SteB Köln-4500115491 - StEB Köln - Support 2025</v>
       </c>
-      <c r="E17" s="59" t="s">
+      <c r="E17" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="59" t="s">
+      <c r="F17" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="57"/>
-    </row>
-    <row r="18" ht="12" customHeight="1" spans="2:7">
-      <c r="B18" s="60" t="s">
+      <c r="G17" s="43"/>
+    </row>
+    <row r="18" spans="2:7" ht="12" customHeight="1">
+      <c r="B18" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="58" t="str">
+      <c r="D18" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Bosch Rexorth-XXXXX- DC - Grownfield S/4 HANA (150)</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="57"/>
-    </row>
-    <row r="19" ht="12" customHeight="1" spans="2:7">
-      <c r="B19" s="60" t="s">
+      <c r="G18" s="43"/>
+    </row>
+    <row r="19" spans="2:7" ht="12" customHeight="1">
+      <c r="B19" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="58" t="str">
+      <c r="D19" s="44" t="str">
         <f t="shared" si="0"/>
         <v>STABILO INTERNATIONAL-1382604-S4_DEVELOPMENT_PROCONARUM - Pos 20</v>
       </c>
-      <c r="E19" s="59" t="s">
+      <c r="E19" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="59" t="s">
+      <c r="F19" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="57"/>
-    </row>
-    <row r="20" ht="12" customHeight="1" spans="2:7">
-      <c r="B20" s="60" t="s">
+      <c r="G19" s="43"/>
+    </row>
+    <row r="20" spans="2:7" ht="12" customHeight="1">
+      <c r="B20" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="58" t="str">
+      <c r="D20" s="44" t="str">
         <f t="shared" si="0"/>
-        <v>kubus IT-Rahmenvertrag 
-</v>
-      </c>
-      <c r="E20" s="59" t="s">
+        <v>kubus IT-Rahmenvertrag</v>
+      </c>
+      <c r="E20" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G20" s="57"/>
-    </row>
-    <row r="21" ht="12" customHeight="1" spans="2:7">
-      <c r="B21" s="60" t="s">
+      <c r="G20" s="43"/>
+    </row>
+    <row r="21" spans="2:7" ht="12" customHeight="1">
+      <c r="B21" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="58" t="str">
+      <c r="D21" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Wacker Chemie AG-1. 9106830021 - UB3 Automation Function
 2. 4550881281_40_MDG_OFFSHORE_Betrieb und
 Support</v>
       </c>
-      <c r="E21" s="66" t="s">
+      <c r="E21" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="57"/>
-    </row>
-    <row r="22" ht="12" customHeight="1" spans="2:7">
-      <c r="B22" s="60" t="s">
+      <c r="G21" s="43"/>
+    </row>
+    <row r="22" spans="2:7" ht="12" customHeight="1">
+      <c r="B22" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="58" t="str">
+      <c r="D22" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Robert Bosch CI /BD-P77-0087017468 - Robert - Bosch BD - MDG/MDC Development (EDEN)</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="67"/>
-    </row>
-    <row r="23" ht="12" customHeight="1" spans="2:7">
-      <c r="B23" s="60" t="s">
+      <c r="G22" s="53"/>
+    </row>
+    <row r="23" spans="2:7" ht="12" customHeight="1">
+      <c r="B23" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="58" t="str">
+      <c r="D23" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Robert Bosch CI /BD-P77-0087017794 - 1 (#518) Bosch UI5 Onshore/Offshore</v>
       </c>
-      <c r="E23" s="68" t="s">
+      <c r="E23" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="57"/>
-    </row>
-    <row r="24" ht="12" customHeight="1" spans="2:7">
-      <c r="B24" s="60" t="s">
+      <c r="G23" s="43"/>
+    </row>
+    <row r="24" spans="2:7" ht="12" customHeight="1">
+      <c r="B24" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="58" t="str">
+      <c r="D24" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Robert Bosch CI /BD-1. P77-0087018149-Pos 1-Robert Bosch CI-S4-DC-grownfield - offshore/onshore
 2. Robert Bosch GmbH - P77-0087016468 Pos2 - S4
 Grownfield Project Offshore</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="57"/>
-    </row>
-    <row r="25" ht="12" customHeight="1" spans="2:7">
-      <c r="B25" s="60" t="s">
+      <c r="G24" s="43"/>
+    </row>
+    <row r="25" spans="2:7" ht="12" customHeight="1">
+      <c r="B25" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="58" t="str">
+      <c r="D25" s="44" t="str">
         <f t="shared" si="0"/>
         <v>STABILO INTERNATIONAL-1427634-10/20 - STABILO - AB MONITOR - offshore/onshore</v>
       </c>
-      <c r="E25" s="68" t="s">
+      <c r="E25" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="57"/>
-    </row>
-    <row r="26" ht="12" customHeight="1" spans="2:7">
-      <c r="B26" s="60" t="s">
+      <c r="G25" s="43"/>
+    </row>
+    <row r="26" spans="2:7" ht="12" customHeight="1">
+      <c r="B26" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="58" t="str">
+      <c r="D26" s="44" t="str">
         <f t="shared" si="0"/>
         <v>SYNTEGON-4550925350-Syntegon-MDG-Analyse</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="57"/>
-    </row>
-    <row r="27" ht="12" customHeight="1" spans="2:7">
-      <c r="B27" s="57" t="s">
+      <c r="G26" s="43"/>
+    </row>
+    <row r="27" spans="2:7" ht="12" customHeight="1">
+      <c r="B27" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="58" t="str">
+      <c r="D27" s="44" t="str">
         <f t="shared" si="0"/>
         <v>SYNTEGON-4550913704-SYNTEGON-ALE-VERTEILUNG 2024</v>
       </c>
-      <c r="E27" s="68" t="s">
+      <c r="E27" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="59" t="s">
+      <c r="F27" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="57"/>
-    </row>
-    <row r="28" ht="12" customHeight="1" spans="2:7">
-      <c r="B28" s="57" t="s">
+      <c r="G27" s="43"/>
+    </row>
+    <row r="28" spans="2:7" ht="12" customHeight="1">
+      <c r="B28" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="58" t="str">
+      <c r="D28" s="44" t="str">
         <f t="shared" si="0"/>
         <v>HUK Coburg-C062497 - HUK - MM Themen</v>
       </c>
-      <c r="E28" s="68" t="s">
+      <c r="E28" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G28" s="57"/>
-    </row>
-    <row r="29" ht="12" customHeight="1" spans="2:7">
-      <c r="B29" s="57" t="s">
+      <c r="G28" s="43"/>
+    </row>
+    <row r="29" spans="2:7" ht="12" customHeight="1">
+      <c r="B29" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C29" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="58" t="str">
+      <c r="D29" s="44" t="str">
         <f t="shared" si="0"/>
         <v>UK Ulm-4550881281_40_MDG_OFFSHORE_Betrieb und</v>
       </c>
-      <c r="E29" s="61" t="s">
+      <c r="E29" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G29" s="57"/>
-    </row>
-    <row r="30" ht="12" customHeight="1" spans="2:7">
-      <c r="B30" s="57" t="s">
+      <c r="G29" s="43"/>
+    </row>
+    <row r="30" spans="2:7" ht="12" customHeight="1">
+      <c r="B30" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="58" t="str">
+      <c r="D30" s="44" t="str">
         <f t="shared" si="0"/>
         <v>Uni Klinikum Düsseldorf UKD-Support</v>
       </c>
-      <c r="E30" s="61" t="s">
+      <c r="E30" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G30" s="57"/>
-    </row>
-    <row r="31" ht="12" customHeight="1" spans="2:7">
-      <c r="B31" s="57" t="s">
+      <c r="G30" s="43"/>
+    </row>
+    <row r="31" spans="2:7" ht="12" customHeight="1">
+      <c r="B31" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="65" t="s">
+      <c r="C31" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="58" t="str">
+      <c r="D31" s="44" t="str">
         <f t="shared" si="0"/>
         <v>kubus IT-1. 72940 - kubus - VDB Enhancement
 2. 37055 - EV/2019/087 - kubus Rahmen</v>
       </c>
-      <c r="E31" s="59" t="s">
+      <c r="E31" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F31" s="59" t="s">
+      <c r="F31" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="57"/>
-    </row>
-    <row r="32" ht="12" customHeight="1" spans="2:7">
-      <c r="B32" s="60" t="s">
+      <c r="G31" s="43"/>
+    </row>
+    <row r="32" spans="2:7" ht="12" customHeight="1">
+      <c r="B32" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="70" t="s">
+      <c r="C32" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="58" t="str">
+      <c r="D32" s="44" t="str">
         <f t="shared" si="0"/>
         <v>CONARUM-proconarum: DocSynAI</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="57"/>
-    </row>
-    <row r="33" ht="12" customHeight="1" spans="2:7">
-      <c r="B33" s="60" t="s">
+      <c r="G32" s="43"/>
+    </row>
+    <row r="33" spans="2:7" ht="12" customHeight="1">
+      <c r="B33" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="71" t="s">
+      <c r="D33" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="E33" s="59" t="s">
+      <c r="E33" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="59" t="s">
+      <c r="F33" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G33" s="57"/>
-    </row>
-    <row r="34" ht="12" customHeight="1" spans="2:7">
-      <c r="B34" s="60" t="s">
+      <c r="G33" s="43"/>
+    </row>
+    <row r="34" spans="2:7" ht="12" customHeight="1">
+      <c r="B34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="C34" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="72" t="s">
+      <c r="D34" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="E34" s="59" t="s">
+      <c r="E34" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G34" s="57"/>
-    </row>
-    <row r="35" ht="12" customHeight="1" spans="2:7">
-      <c r="B35" s="60" t="s">
+      <c r="G34" s="43"/>
+    </row>
+    <row r="35" spans="2:7" ht="12" customHeight="1">
+      <c r="B35" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="72" t="s">
+      <c r="D35" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="59" t="s">
+      <c r="E35" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="59" t="s">
+      <c r="F35" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G35" s="57"/>
-    </row>
-    <row r="36" ht="12" customHeight="1" spans="2:7">
-      <c r="B36" s="60" t="s">
+      <c r="G35" s="43"/>
+    </row>
+    <row r="36" spans="2:7" ht="12" customHeight="1">
+      <c r="B36" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="57" t="s">
+      <c r="C36" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D36" s="72" t="s">
+      <c r="D36" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="E36" s="59" t="s">
+      <c r="E36" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F36" s="59" t="s">
+      <c r="F36" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G36" s="57"/>
-    </row>
-    <row r="37" ht="12" customHeight="1" spans="2:7">
-      <c r="B37" s="60" t="s">
+      <c r="G36" s="43"/>
+    </row>
+    <row r="37" spans="2:7" ht="12" customHeight="1">
+      <c r="B37" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="73" t="s">
+      <c r="C37" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="58" t="str">
+      <c r="D37" s="44" t="str">
         <f t="shared" ref="D37:D45" si="1">B37&amp;"-"&amp;C37</f>
         <v>CONARUM-proconarum Generalize - Activity Management App</v>
       </c>
-      <c r="E37" s="59" t="s">
+      <c r="E37" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F37" s="59" t="s">
+      <c r="F37" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G37" s="57"/>
-    </row>
-    <row r="38" ht="12" customHeight="1" spans="2:7">
-      <c r="B38" s="60" t="s">
+      <c r="G37" s="43"/>
+    </row>
+    <row r="38" spans="2:7" ht="12" customHeight="1">
+      <c r="B38" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="74" t="s">
+      <c r="C38" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="58" t="s">
+      <c r="D38" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="E38" s="59" t="s">
+      <c r="E38" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="59" t="s">
+      <c r="F38" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G38" s="57"/>
-    </row>
-    <row r="39" ht="12" customHeight="1" spans="2:7">
-      <c r="B39" s="60" t="s">
+      <c r="G38" s="43"/>
+    </row>
+    <row r="39" spans="2:7" ht="12" customHeight="1">
+      <c r="B39" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="75" t="s">
+      <c r="C39" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="58" t="str">
+      <c r="D39" s="44" t="str">
         <f t="shared" si="1"/>
         <v>BROSE-1. 4501645393-10/20: Supplier Inquiry - Beratung - Development Offshore
 2. 4501630595-20-BroseAutomatisierung Master Data
 (CN)
 3. 4501568068 - proconarum - Sustainability</v>
       </c>
-      <c r="E39" s="59" t="s">
+      <c r="E39" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="59" t="s">
+      <c r="F39" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G39" s="57"/>
-    </row>
-    <row r="40" ht="12" customHeight="1" spans="2:7">
-      <c r="B40" s="60" t="s">
+      <c r="G39" s="43"/>
+    </row>
+    <row r="40" spans="2:7" ht="12" customHeight="1">
+      <c r="B40" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="57"/>
-      <c r="D40" s="58" t="str">
+      <c r="C40" s="43"/>
+      <c r="D40" s="44" t="str">
         <f t="shared" si="1"/>
         <v>BROSE-</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F40" s="59"/>
-      <c r="G40" s="57"/>
-    </row>
-    <row r="41" ht="12" customHeight="1" spans="2:7">
-      <c r="B41" s="60" t="s">
+      <c r="F40" s="45"/>
+      <c r="G40" s="43"/>
+    </row>
+    <row r="41" spans="2:7" ht="12" customHeight="1">
+      <c r="B41" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="57" t="s">
+      <c r="C41" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="58" t="str">
+      <c r="D41" s="44" t="str">
         <f t="shared" si="1"/>
         <v>biotest-4530036462_Pos.1/2 - biotest - PaaS proconraum - DL ON/OFF</v>
       </c>
-      <c r="E41" s="59" t="s">
+      <c r="E41" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F41" s="59" t="s">
+      <c r="F41" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G41" s="57"/>
-    </row>
-    <row r="42" ht="12" customHeight="1" spans="2:7">
-      <c r="B42" s="60" t="s">
+      <c r="G41" s="43"/>
+    </row>
+    <row r="42" spans="2:7" ht="12" customHeight="1">
+      <c r="B42" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="58" t="str">
+      <c r="C42" s="43"/>
+      <c r="D42" s="44" t="str">
         <f t="shared" si="1"/>
         <v>manrolandgoss-</v>
       </c>
-      <c r="E42" s="59" t="s">
+      <c r="E42" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="59"/>
-      <c r="G42" s="57"/>
-    </row>
-    <row r="43" ht="12" customHeight="1" spans="2:7">
-      <c r="B43" s="60" t="s">
+      <c r="F42" s="45"/>
+      <c r="G42" s="43"/>
+    </row>
+    <row r="43" spans="2:7" ht="12" customHeight="1">
+      <c r="B43" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="57" t="s">
+      <c r="C43" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="58" t="str">
+      <c r="D43" s="44" t="str">
         <f t="shared" si="1"/>
         <v>BROSE-4501676644 - Sync. Ansprechpartner zu proconarum</v>
       </c>
-      <c r="E43" s="59" t="s">
+      <c r="E43" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F43" s="59" t="s">
+      <c r="F43" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G43" s="57"/>
-    </row>
-    <row r="44" ht="12" customHeight="1" spans="2:7">
-      <c r="B44" s="60" t="s">
+      <c r="G43" s="43"/>
+    </row>
+    <row r="44" spans="2:7" ht="12" customHeight="1">
+      <c r="B44" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="72" t="s">
+      <c r="C44" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="58" t="str">
+      <c r="D44" s="44" t="str">
         <f t="shared" si="1"/>
         <v>STABILO INTERNATIONAL-1382604-S4_DEVELOPMENT_PROCONARUM - Pos 20</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="57"/>
-    </row>
-    <row r="45" ht="12" customHeight="1" spans="2:7">
-      <c r="B45" s="60" t="s">
+      <c r="G44" s="43"/>
+    </row>
+    <row r="45" spans="2:7" ht="12" customHeight="1">
+      <c r="B45" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C45" s="60" t="s">
+      <c r="C45" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="58" t="str">
+      <c r="D45" s="44" t="str">
         <f t="shared" si="1"/>
         <v>STABILO INTERNATIONAL-1427636 - STABILO - proconarum PO/POC</v>
       </c>
-      <c r="E45" s="59" t="s">
+      <c r="E45" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="59" t="s">
+      <c r="F45" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G45" s="57"/>
-    </row>
-    <row r="46" ht="12" customHeight="1" spans="2:7">
-      <c r="B46" s="76" t="s">
+      <c r="G45" s="43"/>
+    </row>
+    <row r="46" spans="2:7" ht="12" customHeight="1">
+      <c r="B46" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="76" t="s">
+      <c r="C46" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="76" t="s">
+      <c r="D46" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="77" t="s">
+      <c r="E46" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="F46" s="59" t="s">
+      <c r="F46" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G46" s="57"/>
-    </row>
-    <row r="47" ht="12" customHeight="1"/>
-    <row r="48" ht="12" customHeight="1"/>
+      <c r="G46" s="43"/>
+    </row>
+    <row r="47" spans="2:7" ht="12" customHeight="1"/>
+    <row r="48" spans="2:7" ht="12" customHeight="1"/>
     <row r="49" ht="12" customHeight="1"/>
     <row r="50" ht="12" customHeight="1"/>
     <row r="51" ht="12" customHeight="1"/>
@@ -6059,7 +5340,6 @@
     <row r="1000" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -6067,1281 +5347,1178 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z66"/>
-  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="2.57" customWidth="1"/>
-    <col min="2" max="2" width="12.29" customWidth="1"/>
-    <col min="3" max="3" width="14.43" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
     <col min="4" max="4" width="110" customWidth="1"/>
-    <col min="5" max="5" width="6.57" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="48.57" customWidth="1"/>
-    <col min="8" max="8" width="29.71" customWidth="1"/>
-    <col min="9" max="26" width="11.57" customWidth="1"/>
+    <col min="7" max="7" width="48.5546875" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" customWidth="1"/>
+    <col min="9" max="26" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.75" spans="2:11">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:26" ht="24.6">
+      <c r="B1" s="83" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="J1" s="48" t="s">
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="J1" s="94" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="49" t="s">
+      <c r="K1" s="37" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" ht="15.5" spans="1:26">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:26" ht="15.6">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="48" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="K2" s="49">
+      <c r="K2" s="95">
         <v>22.5</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-    </row>
-    <row r="3" ht="16.25" spans="1:26">
-      <c r="A3" s="3"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="50" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+    </row>
+    <row r="3" spans="1:26" ht="15.6">
+      <c r="A3" s="1"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="K3" s="51">
+      <c r="K3" s="96">
         <v>155.5</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" s="11" t="s">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="B4" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="J4" s="52" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="J4" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="K4" s="53">
+      <c r="K4" s="97">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="12" t="s">
+    <row r="5" spans="1:26">
+      <c r="B5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="12" t="s">
+      <c r="F5" s="86"/>
+      <c r="G5" s="81"/>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="B6" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="4:7">
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="16" t="s">
+      <c r="F6" s="86"/>
+      <c r="G6" s="81"/>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="81"/>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="B8" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="16" t="s">
+      <c r="E8" s="13"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="13"/>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="B9" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="21" t="s">
+      <c r="C9" s="11"/>
+      <c r="D9" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="16" t="s">
+      <c r="E9" s="14"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="B10" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="22" t="s">
+      <c r="C10" s="11"/>
+      <c r="D10" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="16" t="s">
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="B11" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="17" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="25" t="s">
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="B13" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="19" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="14" ht="14.5" spans="2:8">
-      <c r="B14" s="27">
+    <row r="14" spans="1:26" ht="14.4">
+      <c r="B14" s="20">
         <v>46021</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31">
+      <c r="E14" s="23"/>
+      <c r="F14" s="24">
         <v>0.5</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H14" s="33"/>
-    </row>
-    <row r="15" ht="14.5" spans="2:8">
-      <c r="B15" s="27">
+      <c r="H14" s="26"/>
+    </row>
+    <row r="15" spans="1:26" ht="14.4">
+      <c r="B15" s="20">
         <v>46021</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31">
+      <c r="E15" s="23"/>
+      <c r="F15" s="24">
         <v>7.5</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H15" s="33"/>
-    </row>
-    <row r="16" ht="14.5" spans="2:8">
-      <c r="B16" s="27">
+      <c r="H15" s="26"/>
+    </row>
+    <row r="16" spans="1:26" ht="14.4">
+      <c r="B16" s="20">
         <v>45658</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24">
         <v>0.5</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="33"/>
-    </row>
-    <row r="17" ht="14.5" spans="2:8">
-      <c r="B17" s="27">
+      <c r="H16" s="26"/>
+    </row>
+    <row r="17" spans="2:8" ht="14.4">
+      <c r="B17" s="20">
         <v>45658</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31">
+      <c r="E17" s="23"/>
+      <c r="F17" s="24">
         <v>7.5</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="33"/>
-    </row>
-    <row r="18" ht="14.5" spans="2:8">
-      <c r="B18" s="27">
+      <c r="H17" s="26"/>
+    </row>
+    <row r="18" spans="2:8" ht="14.4">
+      <c r="B18" s="20">
         <v>45659</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="31">
+      <c r="E18" s="27"/>
+      <c r="F18" s="24">
         <v>8</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H18" s="33"/>
-    </row>
-    <row r="19" ht="14.5" spans="2:8">
-      <c r="B19" s="27">
+      <c r="H18" s="26"/>
+    </row>
+    <row r="19" spans="2:8" ht="14.4">
+      <c r="B19" s="20">
         <v>45660</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="31">
+      <c r="E19" s="27"/>
+      <c r="F19" s="24">
         <v>0.5</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="33"/>
-    </row>
-    <row r="20" ht="14.5" spans="2:8">
-      <c r="B20" s="27">
+      <c r="H19" s="26"/>
+    </row>
+    <row r="20" spans="2:8" ht="14.4">
+      <c r="B20" s="20">
         <v>45660</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="31">
+      <c r="E20" s="27"/>
+      <c r="F20" s="24">
         <v>7.5</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="33"/>
-    </row>
-    <row r="21" ht="14.5" spans="2:8">
-      <c r="B21" s="27">
+      <c r="H20" s="26"/>
+    </row>
+    <row r="21" spans="2:8" ht="14.4">
+      <c r="B21" s="20">
         <v>45661</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="35"/>
-      <c r="F21" s="31">
+      <c r="E21" s="28"/>
+      <c r="F21" s="24">
         <v>8</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="33"/>
-    </row>
-    <row r="22" ht="14.5" spans="2:8">
-      <c r="B22" s="27">
+      <c r="H21" s="26"/>
+    </row>
+    <row r="22" spans="2:8" ht="14.4">
+      <c r="B22" s="20">
         <v>45662</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="31">
+      <c r="E22" s="28"/>
+      <c r="F22" s="24">
         <v>0.5</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H22" s="33"/>
-    </row>
-    <row r="23" ht="14.5" spans="2:8">
-      <c r="B23" s="27">
+      <c r="H22" s="26"/>
+    </row>
+    <row r="23" spans="2:8" ht="14.4">
+      <c r="B23" s="20">
         <v>45662</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="31">
+      <c r="E23" s="28"/>
+      <c r="F23" s="24">
         <v>7.5</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="33"/>
-    </row>
-    <row r="24" ht="14.5" spans="2:8">
-      <c r="B24" s="27">
+      <c r="H23" s="26"/>
+    </row>
+    <row r="24" spans="2:8" ht="14.4">
+      <c r="B24" s="20">
         <v>45663</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="35"/>
-      <c r="F24" s="31">
+      <c r="E24" s="28"/>
+      <c r="F24" s="24">
         <v>0.5</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="33"/>
-    </row>
-    <row r="25" ht="14.5" spans="2:8">
-      <c r="B25" s="27">
+      <c r="H24" s="26"/>
+    </row>
+    <row r="25" spans="2:8" ht="14.4">
+      <c r="B25" s="20">
         <v>45663</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="35"/>
-      <c r="F25" s="31">
+      <c r="E25" s="28"/>
+      <c r="F25" s="24">
         <v>7.5</v>
       </c>
-      <c r="G25" s="32" t="s">
+      <c r="G25" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H25" s="33"/>
-    </row>
-    <row r="26" ht="14.5" spans="2:8">
-      <c r="B26" s="27">
+      <c r="H25" s="26"/>
+    </row>
+    <row r="26" spans="2:8" ht="14.4">
+      <c r="B26" s="20">
         <v>45665</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="E26" s="35"/>
-      <c r="F26" s="31">
+      <c r="E26" s="28"/>
+      <c r="F26" s="24">
         <v>1</v>
       </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="33"/>
-    </row>
-    <row r="27" ht="14.5" spans="2:8">
-      <c r="B27" s="27">
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
+    </row>
+    <row r="27" spans="2:8" ht="14.4">
+      <c r="B27" s="20">
         <v>45665</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="31">
+      <c r="E27" s="28"/>
+      <c r="F27" s="24">
         <v>0.5</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="33"/>
-    </row>
-    <row r="28" ht="14.5" spans="2:8">
-      <c r="B28" s="27">
+      <c r="H27" s="26"/>
+    </row>
+    <row r="28" spans="2:8" ht="14.4">
+      <c r="B28" s="20">
         <v>45665</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="31">
+      <c r="E28" s="28"/>
+      <c r="F28" s="24">
         <v>3</v>
       </c>
-      <c r="G28" s="32"/>
-      <c r="H28" s="33"/>
-    </row>
-    <row r="29" ht="14.5" spans="2:8">
-      <c r="B29" s="27">
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
+    </row>
+    <row r="29" spans="2:8" ht="14.4">
+      <c r="B29" s="20">
         <v>45665</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="D29" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="35"/>
-      <c r="F29" s="31">
+      <c r="E29" s="28"/>
+      <c r="F29" s="24">
         <v>6.5</v>
       </c>
-      <c r="G29" s="32" t="s">
+      <c r="G29" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H29" s="33"/>
-    </row>
-    <row r="30" ht="14.5" spans="2:8">
-      <c r="B30" s="27">
+      <c r="H29" s="26"/>
+    </row>
+    <row r="30" spans="2:8" ht="14.4">
+      <c r="B30" s="20">
         <v>45666</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D30" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="E30" s="35"/>
-      <c r="F30" s="31">
+      <c r="E30" s="28"/>
+      <c r="F30" s="24">
         <v>2</v>
       </c>
-      <c r="G30" s="32" t="s">
+      <c r="G30" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H30" s="33"/>
-    </row>
-    <row r="31" ht="14.5" spans="2:8">
-      <c r="B31" s="27">
+      <c r="H30" s="26"/>
+    </row>
+    <row r="31" spans="2:8" ht="14.4">
+      <c r="B31" s="20">
         <v>45666</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D31" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E31" s="35"/>
-      <c r="F31" s="31">
+      <c r="E31" s="28"/>
+      <c r="F31" s="24">
         <v>2</v>
       </c>
-      <c r="G31" s="32" t="s">
+      <c r="G31" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H31" s="33"/>
-    </row>
-    <row r="32" ht="14.5" spans="2:8">
-      <c r="B32" s="27">
+      <c r="H31" s="26"/>
+    </row>
+    <row r="32" spans="2:8" ht="14.4">
+      <c r="B32" s="20">
         <v>45666</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D32" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="31">
+      <c r="E32" s="28"/>
+      <c r="F32" s="24">
         <v>4</v>
       </c>
-      <c r="G32" s="32" t="s">
+      <c r="G32" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H32" s="33"/>
-    </row>
-    <row r="33" ht="14.5" spans="2:8">
-      <c r="B33" s="27">
+      <c r="H32" s="26"/>
+    </row>
+    <row r="33" spans="2:8" ht="14.4">
+      <c r="B33" s="20">
         <v>45669</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="31">
+      <c r="E33" s="28"/>
+      <c r="F33" s="24">
         <v>8</v>
       </c>
-      <c r="G33" s="32" t="s">
+      <c r="G33" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H33" s="33"/>
-    </row>
-    <row r="34" ht="14.5" spans="2:8">
-      <c r="B34" s="27">
+      <c r="H33" s="26"/>
+    </row>
+    <row r="34" spans="2:8" ht="14.4">
+      <c r="B34" s="20">
         <v>45669</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="31">
+      <c r="E34" s="28"/>
+      <c r="F34" s="24">
         <v>3</v>
       </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="33"/>
-    </row>
-    <row r="35" ht="14.5" spans="2:8">
-      <c r="B35" s="27">
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
+    </row>
+    <row r="35" spans="2:8" ht="14.4">
+      <c r="B35" s="20">
         <v>45670</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="E35" s="35"/>
-      <c r="F35" s="31">
+      <c r="E35" s="28"/>
+      <c r="F35" s="24">
         <v>4</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H35" s="33"/>
-    </row>
-    <row r="36" ht="14.5" spans="2:8">
-      <c r="B36" s="27">
+      <c r="H35" s="26"/>
+    </row>
+    <row r="36" spans="2:8" ht="14.4">
+      <c r="B36" s="20">
         <v>45670</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="E36" s="35"/>
-      <c r="F36" s="31">
+      <c r="E36" s="28"/>
+      <c r="F36" s="24">
         <v>2</v>
       </c>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H36" s="33"/>
-    </row>
-    <row r="37" ht="14.5" spans="2:8">
-      <c r="B37" s="27">
+      <c r="H36" s="26"/>
+    </row>
+    <row r="37" spans="2:8" ht="14.4">
+      <c r="B37" s="20">
         <v>45670</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="31">
+      <c r="E37" s="28"/>
+      <c r="F37" s="24">
         <v>2</v>
       </c>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H37" s="33"/>
-    </row>
-    <row r="38" ht="14.5" spans="2:8">
-      <c r="B38" s="27">
+      <c r="H37" s="26"/>
+    </row>
+    <row r="38" spans="2:8" ht="14.4">
+      <c r="B38" s="20">
         <v>45671</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="31">
+      <c r="E38" s="28"/>
+      <c r="F38" s="24">
         <v>8</v>
       </c>
-      <c r="G38" s="32" t="s">
+      <c r="G38" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H38" s="33"/>
-    </row>
-    <row r="39" ht="14.5" spans="2:8">
-      <c r="B39" s="27">
+      <c r="H38" s="26"/>
+    </row>
+    <row r="39" spans="2:8" ht="14.4">
+      <c r="B39" s="20">
         <v>45672</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="31">
+      <c r="E39" s="28"/>
+      <c r="F39" s="24">
         <v>7</v>
       </c>
-      <c r="G39" s="32" t="s">
+      <c r="G39" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H39" s="33"/>
-    </row>
-    <row r="40" ht="14.5" spans="2:8">
-      <c r="B40" s="27">
+      <c r="H39" s="26"/>
+    </row>
+    <row r="40" spans="2:8" ht="14.4">
+      <c r="B40" s="20">
         <v>45672</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="E40" s="35"/>
-      <c r="F40" s="31">
+      <c r="E40" s="28"/>
+      <c r="F40" s="24">
         <v>1</v>
       </c>
-      <c r="G40" s="32" t="s">
+      <c r="G40" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H40" s="33"/>
-    </row>
-    <row r="41" ht="14.5" spans="2:8">
-      <c r="B41" s="27">
+      <c r="H40" s="26"/>
+    </row>
+    <row r="41" spans="2:8" ht="14.4">
+      <c r="B41" s="20">
         <v>45673</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C41" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="31">
+      <c r="E41" s="28"/>
+      <c r="F41" s="24">
         <v>1</v>
       </c>
-      <c r="G41" s="32"/>
-      <c r="H41" s="33"/>
-    </row>
-    <row r="42" ht="14.5" spans="2:8">
-      <c r="B42" s="27">
+      <c r="G41" s="25"/>
+      <c r="H41" s="26"/>
+    </row>
+    <row r="42" spans="2:8" ht="14.4">
+      <c r="B42" s="20">
         <v>45673</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="29" t="s">
+      <c r="D42" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="E42" s="35"/>
-      <c r="F42" s="31">
+      <c r="E42" s="28"/>
+      <c r="F42" s="24">
         <v>1</v>
       </c>
-      <c r="G42" s="32" t="s">
+      <c r="G42" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H42" s="33"/>
-    </row>
-    <row r="43" ht="14.5" spans="2:8">
-      <c r="B43" s="27">
+      <c r="H42" s="26"/>
+    </row>
+    <row r="43" spans="2:8" ht="14.4">
+      <c r="B43" s="20">
         <v>45673</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="C43" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D43" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="E43" s="35"/>
-      <c r="F43" s="31">
+      <c r="E43" s="28"/>
+      <c r="F43" s="24">
         <v>6</v>
       </c>
-      <c r="G43" s="32" t="s">
+      <c r="G43" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H43" s="33"/>
-    </row>
-    <row r="44" ht="14.5" spans="2:8">
-      <c r="B44" s="27">
+      <c r="H43" s="26"/>
+    </row>
+    <row r="44" spans="2:8" ht="14.4">
+      <c r="B44" s="20">
         <v>45675</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="35"/>
-      <c r="F44" s="31">
+      <c r="E44" s="28"/>
+      <c r="F44" s="24">
         <v>4</v>
       </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="33"/>
-    </row>
-    <row r="45" ht="14.5" spans="2:8">
-      <c r="B45" s="27">
+      <c r="G44" s="25"/>
+      <c r="H44" s="26"/>
+    </row>
+    <row r="45" spans="2:8" ht="14.4">
+      <c r="B45" s="20">
         <v>45676</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D45" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E45" s="35"/>
-      <c r="F45" s="31">
+      <c r="E45" s="28"/>
+      <c r="F45" s="24">
         <v>3</v>
       </c>
-      <c r="G45" s="32"/>
-      <c r="H45" s="33"/>
-    </row>
-    <row r="46" ht="14.5" spans="2:8">
-      <c r="B46" s="27">
+      <c r="G45" s="25"/>
+      <c r="H45" s="26"/>
+    </row>
+    <row r="46" spans="2:8" ht="14.4">
+      <c r="B46" s="20">
         <v>45676</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="29" t="s">
+      <c r="D46" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="E46" s="35"/>
-      <c r="F46" s="31">
+      <c r="E46" s="28"/>
+      <c r="F46" s="24">
         <v>8</v>
       </c>
-      <c r="G46" s="32" t="s">
+      <c r="G46" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H46" s="33"/>
-    </row>
-    <row r="47" ht="14.5" spans="2:8">
-      <c r="B47" s="27">
+      <c r="H46" s="26"/>
+    </row>
+    <row r="47" spans="2:8" ht="14.4">
+      <c r="B47" s="20">
         <v>45677</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D47" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="31">
+      <c r="E47" s="28"/>
+      <c r="F47" s="24">
         <v>1</v>
       </c>
-      <c r="G47" s="32" t="s">
+      <c r="G47" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H47" s="33"/>
-    </row>
-    <row r="48" ht="14.5" spans="2:8">
-      <c r="B48" s="27">
+      <c r="H47" s="26"/>
+    </row>
+    <row r="48" spans="2:8" ht="14.4">
+      <c r="B48" s="20">
         <v>45677</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="C48" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="29" t="s">
+      <c r="D48" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="E48" s="35"/>
-      <c r="F48" s="31">
+      <c r="E48" s="28"/>
+      <c r="F48" s="24">
         <v>7</v>
       </c>
-      <c r="G48" s="32" t="s">
+      <c r="G48" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H48" s="33"/>
-    </row>
-    <row r="49" ht="14.5" spans="2:8">
-      <c r="B49" s="27">
+      <c r="H48" s="26"/>
+    </row>
+    <row r="49" spans="2:8" ht="14.4">
+      <c r="B49" s="20">
         <v>45678</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="29" t="s">
+      <c r="D49" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="E49" s="35"/>
-      <c r="F49" s="31">
+      <c r="E49" s="28"/>
+      <c r="F49" s="24">
         <v>8</v>
       </c>
-      <c r="G49" s="32" t="s">
+      <c r="G49" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H49" s="33"/>
-    </row>
-    <row r="50" ht="14.5" spans="2:8">
-      <c r="B50" s="27">
+      <c r="H49" s="26"/>
+    </row>
+    <row r="50" spans="2:8" ht="14.4">
+      <c r="B50" s="20">
         <v>45679</v>
       </c>
-      <c r="C50" s="28" t="s">
+      <c r="C50" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="29" t="s">
+      <c r="D50" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="E50" s="35"/>
-      <c r="F50" s="31">
+      <c r="E50" s="28"/>
+      <c r="F50" s="24">
         <v>1</v>
       </c>
-      <c r="G50" s="32" t="s">
+      <c r="G50" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H50" s="33"/>
-    </row>
-    <row r="51" ht="14.5" spans="2:8">
-      <c r="B51" s="27">
+      <c r="H50" s="26"/>
+    </row>
+    <row r="51" spans="2:8" ht="14.4">
+      <c r="B51" s="20">
         <v>45679</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="29" t="s">
+      <c r="D51" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="E51" s="35"/>
-      <c r="F51" s="31">
+      <c r="E51" s="28"/>
+      <c r="F51" s="24">
         <v>7</v>
       </c>
-      <c r="G51" s="32" t="s">
+      <c r="G51" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H51" s="33"/>
-    </row>
-    <row r="52" ht="14.5" spans="2:8">
-      <c r="B52" s="27">
+      <c r="H51" s="26"/>
+    </row>
+    <row r="52" spans="2:8" ht="14.4">
+      <c r="B52" s="20">
         <v>45679</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="29" t="s">
+      <c r="D52" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E52" s="35"/>
-      <c r="F52" s="31">
+      <c r="E52" s="28"/>
+      <c r="F52" s="24">
         <v>3</v>
       </c>
-      <c r="G52" s="32"/>
-      <c r="H52" s="33"/>
-    </row>
-    <row r="53" ht="14.5" spans="2:8">
-      <c r="B53" s="27">
+      <c r="G52" s="25"/>
+      <c r="H52" s="26"/>
+    </row>
+    <row r="53" spans="2:8" ht="14.4">
+      <c r="B53" s="20">
         <v>45680</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="29" t="s">
+      <c r="D53" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="E53" s="35"/>
-      <c r="F53" s="31">
+      <c r="E53" s="28"/>
+      <c r="F53" s="24">
         <v>2</v>
       </c>
-      <c r="G53" s="32"/>
-      <c r="H53" s="33"/>
-    </row>
-    <row r="54" ht="14.5" spans="2:8">
-      <c r="B54" s="27">
+      <c r="G53" s="25"/>
+      <c r="H53" s="26"/>
+    </row>
+    <row r="54" spans="2:8" ht="14.4">
+      <c r="B54" s="20">
         <v>45683</v>
       </c>
-      <c r="C54" s="28" t="s">
+      <c r="C54" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="29" t="s">
+      <c r="D54" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="E54" s="35"/>
-      <c r="F54" s="31">
+      <c r="E54" s="28"/>
+      <c r="F54" s="24">
         <v>8</v>
       </c>
-      <c r="G54" s="32" t="s">
+      <c r="G54" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H54" s="33"/>
-    </row>
-    <row r="55" ht="14.5" spans="2:8">
-      <c r="B55" s="27">
+      <c r="H54" s="26"/>
+    </row>
+    <row r="55" spans="2:8" ht="14.4">
+      <c r="B55" s="20">
         <v>45684</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C55" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D55" s="29" t="s">
+      <c r="D55" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="E55" s="35"/>
-      <c r="F55" s="31">
+      <c r="E55" s="28"/>
+      <c r="F55" s="24">
         <v>1.5</v>
       </c>
-      <c r="G55" s="32"/>
-      <c r="H55" s="33"/>
-    </row>
-    <row r="56" ht="14.5" spans="2:8">
-      <c r="B56" s="27">
+      <c r="G55" s="25"/>
+      <c r="H55" s="26"/>
+    </row>
+    <row r="56" spans="2:8" ht="14.4">
+      <c r="B56" s="20">
         <v>45684</v>
       </c>
-      <c r="C56" s="28" t="s">
+      <c r="C56" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="29" t="s">
+      <c r="D56" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="E56" s="35"/>
-      <c r="F56" s="31">
+      <c r="E56" s="28"/>
+      <c r="F56" s="24">
         <v>0.5</v>
       </c>
-      <c r="G56" s="32" t="s">
+      <c r="G56" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H56" s="33"/>
-    </row>
-    <row r="57" ht="14.5" spans="2:8">
-      <c r="B57" s="27">
+      <c r="H56" s="26"/>
+    </row>
+    <row r="57" spans="2:8" ht="14.4">
+      <c r="B57" s="20">
         <v>45684</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D57" s="29" t="s">
+      <c r="D57" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E57" s="35"/>
-      <c r="F57" s="31">
+      <c r="E57" s="28"/>
+      <c r="F57" s="24">
         <v>0.5</v>
       </c>
-      <c r="G57" s="32" t="s">
+      <c r="G57" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H57" s="33"/>
-    </row>
-    <row r="58" ht="14.5" spans="2:8">
-      <c r="B58" s="27">
+      <c r="H57" s="26"/>
+    </row>
+    <row r="58" spans="2:8" ht="14.4">
+      <c r="B58" s="20">
         <v>45684</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="C58" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="29" t="s">
+      <c r="D58" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="E58" s="35"/>
-      <c r="F58" s="31">
+      <c r="E58" s="28"/>
+      <c r="F58" s="24">
         <v>4.5</v>
       </c>
-      <c r="G58" s="32" t="s">
+      <c r="G58" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H58" s="33"/>
-    </row>
-    <row r="59" ht="14.5" spans="2:8">
-      <c r="B59" s="27">
+      <c r="H58" s="26"/>
+    </row>
+    <row r="59" spans="2:8" ht="14.4">
+      <c r="B59" s="20">
         <v>45684</v>
       </c>
-      <c r="C59" s="28" t="s">
+      <c r="C59" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D59" s="29" t="s">
+      <c r="D59" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="E59" s="35"/>
-      <c r="F59" s="31">
+      <c r="E59" s="28"/>
+      <c r="F59" s="24">
         <v>1</v>
       </c>
-      <c r="G59" s="32"/>
-      <c r="H59" s="33"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="26"/>
     </row>
     <row r="60" spans="2:8">
-      <c r="B60" s="36" t="s">
+      <c r="B60" s="89" t="s">
         <v>149</v>
       </c>
-      <c r="C60" s="37"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="40">
+      <c r="C60" s="90"/>
+      <c r="D60" s="91"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="30">
         <f>SUM(F14:F59)</f>
         <v>178</v>
       </c>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
     </row>
     <row r="61" spans="2:8">
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="41">
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="31">
         <f>F60/8</f>
         <v>22.25</v>
       </c>
-      <c r="G61" s="16" t="s">
+      <c r="G61" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="H61" s="16"/>
+      <c r="H61" s="11"/>
     </row>
     <row r="62" spans="2:8">
-      <c r="B62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-    </row>
-    <row r="63" ht="13.75" spans="5:6">
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
+      <c r="B62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+    </row>
+    <row r="63" spans="2:8">
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
     </row>
     <row r="64" spans="2:8">
-      <c r="B64" s="44" t="s">
+      <c r="B64" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="C64" s="44"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="45"/>
-      <c r="G64" s="46" t="s">
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="35"/>
+      <c r="G64" s="92" t="s">
         <v>152</v>
       </c>
-      <c r="H64" s="47"/>
+      <c r="H64" s="93"/>
     </row>
     <row r="66" spans="2:2">
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="9" t="s">
         <v>153</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="G64:H64"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="G64:H64"/>
   </mergeCells>
-  <conditionalFormatting sqref="C15">
-    <cfRule type="containsText" dxfId="6" priority="19" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19">
-    <cfRule type="containsText" dxfId="6" priority="18" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C19)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
-    <cfRule type="containsText" dxfId="6" priority="17" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C23)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C25">
-    <cfRule type="containsText" dxfId="6" priority="16" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C25)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29">
-    <cfRule type="containsText" dxfId="6" priority="15" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C29)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C31">
-    <cfRule type="containsText" dxfId="6" priority="14" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C31)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32">
-    <cfRule type="containsText" dxfId="6" priority="13" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C32)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C33">
-    <cfRule type="containsText" dxfId="6" priority="9" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C36">
-    <cfRule type="containsText" dxfId="6" priority="28" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C36)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C37">
-    <cfRule type="containsText" dxfId="6" priority="12" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C37)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C40">
-    <cfRule type="containsText" dxfId="6" priority="27" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C40)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C42">
-    <cfRule type="containsText" dxfId="6" priority="26" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C42)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C43">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C43)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C44">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C44)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C46">
-    <cfRule type="containsText" dxfId="6" priority="6" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C46)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C48">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C48)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C49">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C49)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C51">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C51)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C52">
-    <cfRule type="containsText" dxfId="6" priority="20" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C52)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C55">
-    <cfRule type="containsText" dxfId="6" priority="21" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C56">
-    <cfRule type="containsText" dxfId="6" priority="23" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C56)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C57:C58">
-    <cfRule type="containsText" dxfId="6" priority="22" operator="between" text="Papierkram">
-      <formula>NOT(ISERROR(SEARCH("Papierkram",C57)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C14 C16:C18 C20:C22 C24 C26:C28 C30 C34:C35 C41 C38:C39 C45 C47 C50 C53:C54 C59:C1016">
-    <cfRule type="containsText" dxfId="6" priority="29" operator="between" text="Papierkram">
+  <conditionalFormatting sqref="C1:C1016">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Papierkram">
       <formula>NOT(ISERROR(SEARCH("Papierkram",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C14:C59">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C14:C59" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Papierkram,Internal,Others"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G14:G59">
-      <formula1>Legend!$C$3:$C$46</formula1>
-    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.393700787401575" right="0.433070866141732" top="0.531666666666667" bottom="0.78740157480315" header="0" footer="0"/>
+  <pageMargins left="0.39370078740157499" right="0.43307086614173201" top="0.53166666666666695" bottom="0.78740157480314998" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="67" orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
+          <x14:formula1>
+            <xm:f>Legend!$C$3:$C$46</xm:f>
+          </x14:formula1>
+          <xm:sqref>G14:G59</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>